--- a/internal_doc/05.测试设计/story/loadCS/loadCS测试用例_JS（loadCS及其他接口）.xlsx
+++ b/internal_doc/05.测试设计/story/loadCS/loadCS测试用例_JS（loadCS及其他接口）.xlsx
@@ -780,7 +780,9 @@
       <c r="H3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="3"/>
+      <c r="I3" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="4" spans="1:9" ht="27">
       <c r="A4" s="1" t="s">
@@ -804,7 +806,9 @@
       <c r="H4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="3"/>
+      <c r="I4" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="5" spans="1:9" ht="67.5">
       <c r="A5" s="1" t="s">
@@ -828,7 +832,9 @@
       <c r="H5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="3"/>
+      <c r="I5" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="6" spans="1:9" ht="67.5">
       <c r="A6" s="1" t="s">
@@ -878,7 +884,9 @@
       <c r="H7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I7" s="3"/>
+      <c r="I7" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="8" spans="1:9" ht="81">
       <c r="A8" s="1" t="s">
